--- a/data/trans_orig/ESTUDIOS-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2007</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44523</t>
+          <t>43788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>71908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>39855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>67702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92942</t>
+          <t>90290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128046</t>
+          <t>127835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120832</t>
+          <t>120784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153116</t>
+          <t>154828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110960</t>
+          <t>110908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143986</t>
+          <t>144945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242704</t>
+          <t>241943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290908</t>
+          <t>288581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64658</t>
+          <t>63600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93458</t>
+          <t>93477</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65454</t>
+          <t>66327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96459</t>
+          <t>96782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>136758</t>
+          <t>137005</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180556</t>
+          <t>181464</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65845</t>
+          <t>66117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>101992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>27070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98524</t>
+          <t>99654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144759</t>
+          <t>142688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>211443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>257775</t>
+          <t>256758</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>228819</t>
+          <t>227299</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276554</t>
+          <t>271719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>452730</t>
+          <t>455000</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>518059</t>
+          <t>518683</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152483</t>
+          <t>154162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197728</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192459</t>
+          <t>193437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>239508</t>
+          <t>235690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>360862</t>
+          <t>360298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>423239</t>
+          <t>420624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,19%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68440</t>
+          <t>67294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>62067</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>83379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120273</t>
+          <t>120336</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162307</t>
+          <t>162071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197865</t>
+          <t>197198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136695</t>
+          <t>135777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172149</t>
+          <t>172146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308406</t>
+          <t>306351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361197</t>
+          <t>358258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70898</t>
+          <t>70550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101279</t>
+          <t>103201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117193</t>
+          <t>116772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152248</t>
+          <t>151364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194387</t>
+          <t>194847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244024</t>
+          <t>242927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47048</t>
+          <t>47656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75339</t>
+          <t>74854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>59507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91209</t>
+          <t>88344</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114627</t>
+          <t>112535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154435</t>
+          <t>154966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191937</t>
+          <t>191300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229450</t>
+          <t>227829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154299</t>
+          <t>153041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191164</t>
+          <t>188986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354958</t>
+          <t>355738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406846</t>
+          <t>408174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72382</t>
+          <t>72864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104149</t>
+          <t>103698</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109341</t>
+          <t>109644</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145839</t>
+          <t>143926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>191546</t>
+          <t>191796</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>239823</t>
+          <t>239678</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>34925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>37924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66606</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64247</t>
+          <t>64533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91992</t>
+          <t>91807</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76335</t>
+          <t>74119</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103775</t>
+          <t>105213</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148067</t>
+          <t>146451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>187496</t>
+          <t>186558</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85776</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113282</t>
+          <t>115053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79147</t>
+          <t>78972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108191</t>
+          <t>108621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172452</t>
+          <t>174877</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213557</t>
+          <t>214726</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>41175</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67734</t>
+          <t>68533</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48011</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>72451</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>104532</t>
+          <t>103998</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132734</t>
+          <t>131725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163917</t>
+          <t>164606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118563</t>
+          <t>118280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153102</t>
+          <t>151085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262440</t>
+          <t>261396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309683</t>
+          <t>309079</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82798</t>
+          <t>83158</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91814</t>
+          <t>91643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123937</t>
+          <t>124448</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>154741</t>
+          <t>155841</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>198030</t>
+          <t>198368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84505</t>
+          <t>86813</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>124375</t>
+          <t>125126</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74110</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110287</t>
+          <t>108714</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>168812</t>
+          <t>169066</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>223357</t>
+          <t>225467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>321105</t>
+          <t>320504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>370538</t>
+          <t>369519</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>278602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>327945</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>615507</t>
+          <t>614811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>688084</t>
+          <t>687532</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,86%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145431</t>
+          <t>147146</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>190079</t>
+          <t>188690</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>218667</t>
+          <t>217681</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>265793</t>
+          <t>266628</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>375201</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>441144</t>
+          <t>441340</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>96224</t>
+          <t>97432</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>136278</t>
+          <t>137192</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>96845</t>
+          <t>98642</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>137171</t>
+          <t>139980</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205182</t>
+          <t>205052</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>261918</t>
+          <t>262614</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>327151</t>
+          <t>329225</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>383509</t>
+          <t>383404</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>326689</t>
+          <t>325619</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>384259</t>
+          <t>382256</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>670481</t>
+          <t>671439</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>750967</t>
+          <t>746701</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>247941</t>
+          <t>247724</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>299982</t>
+          <t>298478</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>285295</t>
+          <t>282903</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>340606</t>
+          <t>341282</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>547165</t>
+          <t>543909</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>623762</t>
+          <t>623552</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>504486</t>
+          <t>509292</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>593968</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>438292</t>
+          <t>438952</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>520395</t>
+          <t>516263</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>973294</t>
+          <t>966748</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1091586</t>
+          <t>1094736</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1635903</t>
+          <t>1627685</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1751126</t>
+          <t>1750356</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1529325</t>
+          <t>1530722</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1646395</t>
+          <t>1646221</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3190490</t>
+          <t>3194336</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3359739</t>
+          <t>3362410</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>973795</t>
+          <t>983225</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1084056</t>
+          <t>1088008</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1254028</t>
+          <t>1252523</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1366719</t>
+          <t>1367276</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2267662</t>
+          <t>2259779</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2423993</t>
+          <t>2412654</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2012</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55530</t>
+          <t>54392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45584</t>
+          <t>44754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>56902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93308</t>
+          <t>89130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145786</t>
+          <t>146014</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180999</t>
+          <t>179589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131777</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168685</t>
+          <t>169283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>290397</t>
+          <t>286617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339243</t>
+          <t>338630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71885</t>
+          <t>73434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105789</t>
+          <t>104657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88551</t>
+          <t>86263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122780</t>
+          <t>121749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170731</t>
+          <t>167114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215377</t>
+          <t>215384</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67581</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37137</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64246</t>
+          <t>65791</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80332</t>
+          <t>80035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124323</t>
+          <t>122043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>255603</t>
+          <t>256319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>304601</t>
+          <t>302640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>224023</t>
+          <t>219855</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>271242</t>
+          <t>266869</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>490751</t>
+          <t>489744</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>557453</t>
+          <t>557667</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153449</t>
+          <t>154970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197994</t>
+          <t>197680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203610</t>
+          <t>204681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249973</t>
+          <t>251771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>370413</t>
+          <t>370400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>438664</t>
+          <t>438105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34896</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61326</t>
+          <t>61825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34374</t>
+          <t>34414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>62190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76029</t>
+          <t>75535</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115390</t>
+          <t>113560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153251</t>
+          <t>152615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190415</t>
+          <t>190179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120231</t>
+          <t>117196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156680</t>
+          <t>155799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282681</t>
+          <t>283289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337231</t>
+          <t>335888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88465</t>
+          <t>89713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122734</t>
+          <t>123847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>138954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175883</t>
+          <t>176039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234598</t>
+          <t>236286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287740</t>
+          <t>286308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58710</t>
+          <t>58072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49091</t>
+          <t>49439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79605</t>
+          <t>79543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87438</t>
+          <t>89259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128519</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>226509</t>
+          <t>226790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>265686</t>
+          <t>265850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166698</t>
+          <t>165936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205709</t>
+          <t>207192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>404158</t>
+          <t>400825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459895</t>
+          <t>458136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66896</t>
+          <t>67215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99134</t>
+          <t>100495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>120477</t>
+          <t>122025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158792</t>
+          <t>161184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>198276</t>
+          <t>195149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>251914</t>
+          <t>249359</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43702</t>
+          <t>45082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37558</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71884</t>
+          <t>74002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125555</t>
+          <t>123240</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>152333</t>
+          <t>151465</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100333</t>
+          <t>100229</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130318</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>233516</t>
+          <t>233694</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>273642</t>
+          <t>275854</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62789</t>
+          <t>64205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92415</t>
+          <t>92007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102980</t>
+          <t>102566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141222</t>
+          <t>141312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55534</t>
+          <t>52861</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47985</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59791</t>
+          <t>59481</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95491</t>
+          <t>93524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120883</t>
+          <t>120464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155479</t>
+          <t>154619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>96269</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129980</t>
+          <t>127732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223486</t>
+          <t>228387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272774</t>
+          <t>274914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,8%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79787</t>
+          <t>79968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112175</t>
+          <t>111673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115293</t>
+          <t>114104</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146602</t>
+          <t>147896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>203850</t>
+          <t>205821</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>251809</t>
+          <t>250743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>96831</t>
+          <t>96370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138755</t>
+          <t>138003</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>79273</t>
+          <t>81466</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>119676</t>
+          <t>122468</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>187730</t>
+          <t>187052</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>245047</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>326179</t>
+          <t>328952</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>380743</t>
+          <t>382879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>320503</t>
+          <t>318786</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>375680</t>
+          <t>372840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>661831</t>
+          <t>660526</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>738350</t>
+          <t>735894</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>168353</t>
+          <t>168835</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>219715</t>
+          <t>215713</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>219778</t>
+          <t>220856</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>274703</t>
+          <t>274077</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>405951</t>
+          <t>403027</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>476269</t>
+          <t>478482</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>89958</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>132106</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,82 +8280,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>16,88%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>106756</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>85086</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>127164</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>217253</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>188675</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>249996</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>11,8%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>106756</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>88588</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>130557</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>217253</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>186836</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>245350</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>446304</t>
+          <t>447536</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>504787</t>
+          <t>503599</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>432093</t>
+          <t>430670</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>490859</t>
+          <t>491911</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>897889</t>
+          <t>894890</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>979385</t>
+          <t>980253</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>167676</t>
+          <t>166698</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>216778</t>
+          <t>218174</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>226046</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>281466</t>
+          <t>281034</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>407691</t>
+          <t>407858</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>480748</t>
+          <t>483311</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>435808</t>
+          <t>441643</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>520932</t>
+          <t>524800</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>418653</t>
+          <t>416935</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>497333</t>
+          <t>497515</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>879508</t>
+          <t>883662</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1003061</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1905733</t>
+          <t>1904778</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2025050</t>
+          <t>2023077</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1696621</t>
+          <t>1699465</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1815997</t>
+          <t>1818182</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3635073</t>
+          <t>3635571</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3803877</t>
+          <t>3806724</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>925115</t>
+          <t>919538</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1030407</t>
+          <t>1034254</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1275324</t>
+          <t>1276796</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1390487</t>
+          <t>1394574</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2236082</t>
+          <t>2228586</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2391923</t>
+          <t>2393811</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2016</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69277</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>68918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103485</t>
+          <t>104679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161816</t>
+          <t>162126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196304</t>
+          <t>197581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132094</t>
+          <t>132189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168984</t>
+          <t>165643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305105</t>
+          <t>304696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>353909</t>
+          <t>352653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66797</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98418</t>
+          <t>96739</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69035</t>
+          <t>69452</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100032</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>143602</t>
+          <t>141874</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>186069</t>
+          <t>187501</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>34937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>62525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43090</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70769</t>
+          <t>70476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86372</t>
+          <t>84845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125555</t>
+          <t>122816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311609</t>
+          <t>309793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>355875</t>
+          <t>353381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>263924</t>
+          <t>264607</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>311875</t>
+          <t>308961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>588547</t>
+          <t>586129</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>652456</t>
+          <t>651405</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104804</t>
+          <t>104503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142475</t>
+          <t>143805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156631</t>
+          <t>158327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202060</t>
+          <t>200615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272192</t>
+          <t>273042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332622</t>
+          <t>333328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35208</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>60971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>69047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83939</t>
+          <t>83274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120933</t>
+          <t>121461</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182332</t>
+          <t>181982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218093</t>
+          <t>214694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162785</t>
+          <t>162417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200077</t>
+          <t>198604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>354919</t>
+          <t>352661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>406163</t>
+          <t>404927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59033</t>
+          <t>59678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89199</t>
+          <t>87983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82678</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118465</t>
+          <t>117043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151504</t>
+          <t>150009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196050</t>
+          <t>195786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>53380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83434</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52038</t>
+          <t>51713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82382</t>
+          <t>80797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114021</t>
+          <t>114435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>159564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198143</t>
+          <t>199065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>236979</t>
+          <t>236964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180196</t>
+          <t>180609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222024</t>
+          <t>220815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389659</t>
+          <t>392406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>445078</t>
+          <t>447397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66545</t>
+          <t>65968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99038</t>
+          <t>98432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100183</t>
+          <t>99619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137642</t>
+          <t>138105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>175163</t>
+          <t>176192</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>224890</t>
+          <t>226163</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37614</t>
+          <t>35597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28990</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84591</t>
+          <t>84746</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>112777</t>
+          <t>112813</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102945</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130185</t>
+          <t>130810</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>194491</t>
+          <t>196418</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>237015</t>
+          <t>237040</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67448</t>
+          <t>68837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95077</t>
+          <t>96643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>71930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98780</t>
+          <t>98779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148758</t>
+          <t>146927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187882</t>
+          <t>186851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>30692</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55768</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>27298</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>63524</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97396</t>
+          <t>98676</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>126788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>159098</t>
+          <t>159390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129621</t>
+          <t>128410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161438</t>
+          <t>160311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263810</t>
+          <t>266042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>311749</t>
+          <t>313471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62387</t>
+          <t>63431</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91858</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74938</t>
+          <t>76524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107291</t>
+          <t>107635</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146831</t>
+          <t>145745</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191783</t>
+          <t>190590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129378</t>
+          <t>128222</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>176927</t>
+          <t>173682</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>124449</t>
+          <t>124654</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166451</t>
+          <t>169788</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>263008</t>
+          <t>263698</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>328597</t>
+          <t>328736</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>372840</t>
+          <t>372289</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>426206</t>
+          <t>425617</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>356771</t>
+          <t>358936</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>411541</t>
+          <t>413484</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>748108</t>
+          <t>743756</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>824838</t>
+          <t>820943</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87054</t>
+          <t>86002</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>124004</t>
+          <t>122950</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140615</t>
+          <t>137530</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>185921</t>
+          <t>184206</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>231717</t>
+          <t>236092</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>294665</t>
+          <t>296202</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>114853</t>
+          <t>113958</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>157717</t>
+          <t>158891</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>100755</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>144437</t>
+          <t>145759</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>226116</t>
+          <t>228893</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>289347</t>
+          <t>290398</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>476735</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>530372</t>
+          <t>531479</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>490581</t>
+          <t>489720</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>545761</t>
+          <t>547351</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>982938</t>
+          <t>982491</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1064830</t>
+          <t>1063178</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113831</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>156812</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>154196</t>
+          <t>151529</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>203850</t>
+          <t>203484</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277932</t>
+          <t>279997</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>345096</t>
+          <t>345656</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>503587</t>
+          <t>505598</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>592706</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>504970</t>
+          <t>503545</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>597590</t>
+          <t>590770</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1037197</t>
+          <t>1043913</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1157595</t>
+          <t>1163837</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2024470</t>
+          <t>2019681</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2136866</t>
+          <t>2137122</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1929646</t>
+          <t>1927529</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2051783</t>
+          <t>2048841</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3973205</t>
+          <t>3989228</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4138121</t>
+          <t>4149508</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>708414</t>
+          <t>701210</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>801609</t>
+          <t>799716</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>940730</t>
+          <t>939460</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1055023</t>
+          <t>1053606</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1677152</t>
+          <t>1675399</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1822310</t>
+          <t>1818983</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2023</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44221</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74044</t>
+          <t>74642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56784</t>
+          <t>56033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83857</t>
+          <t>82043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>108887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150757</t>
+          <t>147272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170243</t>
+          <t>171401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210451</t>
+          <t>211700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146548</t>
+          <t>147071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174418</t>
+          <t>175943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325626</t>
+          <t>327105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376127</t>
+          <t>376502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>80661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>69659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102813</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>142091</t>
+          <t>143663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>74820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118458</t>
+          <t>124238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61233</t>
+          <t>60922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>91268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144847</t>
+          <t>143007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198883</t>
+          <t>195617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>343678</t>
+          <t>343832</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>393363</t>
+          <t>396436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>306382</t>
+          <t>306214</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>345121</t>
+          <t>343912</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>665003</t>
+          <t>664595</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>726800</t>
+          <t>730187</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>37576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>65285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100363</t>
+          <t>101457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132396</t>
+          <t>135534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144010</t>
+          <t>144369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187344</t>
+          <t>189471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52703</t>
+          <t>52323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38728</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59893</t>
+          <t>60583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73500</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106046</t>
+          <t>105350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190818</t>
+          <t>190062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223605</t>
+          <t>222258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200409</t>
+          <t>199205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228794</t>
+          <t>229703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399053</t>
+          <t>402252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444215</t>
+          <t>443176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>81569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71722</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95639</t>
+          <t>94283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133611</t>
+          <t>133580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168735</t>
+          <t>168562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82911</t>
+          <t>79989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124206</t>
+          <t>123036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58411</t>
+          <t>64455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134082</t>
+          <t>135880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150366</t>
+          <t>145548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244706</t>
+          <t>244850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130075</t>
+          <t>128739</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176196</t>
+          <t>173289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>227146</t>
+          <t>225931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349152</t>
+          <t>354332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372699</t>
+          <t>372822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>518625</t>
+          <t>534915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74745</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56224</t>
+          <t>53528</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118601</t>
+          <t>118694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112454</t>
+          <t>112098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180824</t>
+          <t>180028</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>41380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>61347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41990</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>58753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89765</t>
+          <t>88940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116384</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>106981</t>
+          <t>107958</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>127969</t>
+          <t>128654</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124522</t>
+          <t>125990</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>143491</t>
+          <t>144696</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>237157</t>
+          <t>239241</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>267207</t>
+          <t>267246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59641</t>
+          <t>59642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>67362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95295</t>
+          <t>95978</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161432</t>
+          <t>161214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189933</t>
+          <t>189966</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132432</t>
+          <t>132994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>158836</t>
+          <t>158336</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>302648</t>
+          <t>304355</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>341227</t>
+          <t>341263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73796</t>
+          <t>74419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52662</t>
+          <t>53209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72317</t>
+          <t>72160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>108167</t>
+          <t>108710</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138264</t>
+          <t>138498</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>172055</t>
+          <t>167651</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68902</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>224221</t>
+          <t>223274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>185727</t>
+          <t>184680</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>368869</t>
+          <t>366977</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>360899</t>
+          <t>365315</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>419835</t>
+          <t>422109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>477637</t>
+          <t>478057</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>728998</t>
+          <t>702880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>869741</t>
+          <t>871289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1160681</t>
+          <t>1157685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71561</t>
+          <t>72847</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108073</t>
+          <t>108001</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>56762</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151367</t>
+          <t>153093</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>124364</t>
+          <t>126353</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>240614</t>
+          <t>239912</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178377</t>
+          <t>177948</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>88028</t>
+          <t>87266</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>120981</t>
+          <t>119644</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>137485</t>
+          <t>142478</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>274864</t>
+          <t>274993</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>586064</t>
+          <t>585726</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>820467</t>
+          <t>815498</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>378451</t>
+          <t>381232</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>424990</t>
+          <t>426086</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>979777</t>
+          <t>981327</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1300744</t>
+          <t>1303856</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>53236</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>167160</t>
+          <t>167552</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>190036</t>
+          <t>191183</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>234212</t>
+          <t>231225</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>194774</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>394874</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>501443</t>
+          <t>506288</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>718854</t>
+          <t>714052</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>540195</t>
+          <t>534566</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>721328</t>
+          <t>724014</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1124701</t>
+          <t>1142504</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1416665</t>
+          <t>1412003</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2184617</t>
+          <t>2180364</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2548430</t>
+          <t>2546506</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2118079</t>
+          <t>2123130</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2504404</t>
+          <t>2513248</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,47 +17564,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>4528150</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>4342465</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4870359</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>63,73%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>68,54%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>4528150</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>4338019</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>4883446</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>400712</t>
+          <t>400690</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>570666</t>
+          <t>574038</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>612161</t>
+          <t>616359</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>826788</t>
+          <t>820730</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1092163</t>
+          <t>1099221</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1366081</t>
+          <t>1372437</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
